--- a/config/config_table.xlsx
+++ b/config/config_table.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="设计" sheetId="35" r:id="rId1"/>
@@ -14,7 +14,8 @@
     <sheet name="buff" sheetId="41" r:id="rId5"/>
     <sheet name="debuff" sheetId="39" r:id="rId6"/>
     <sheet name="boss_debuff" sheetId="40" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId8"/>
+    <sheet name="dice_multiplier" sheetId="42" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="709">
   <si>
     <t>流程：</t>
   </si>
@@ -1471,6 +1472,30 @@
   </si>
   <si>
     <t>res://scripts/buff/attack_score_down_buff.gd</t>
+  </si>
+  <si>
+    <t>骰子数量</t>
+  </si>
+  <si>
+    <t>dice_sum</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>shunzi</t>
+  </si>
+  <si>
+    <t>tongse</t>
+  </si>
+  <si>
+    <t>duizi</t>
+  </si>
+  <si>
+    <t>tongshun</t>
+  </si>
+  <si>
+    <t>tongdui</t>
   </si>
   <si>
     <t>ID</t>
@@ -6038,8 +6063,8 @@
     <col min="1" max="1" width="34.75" customWidth="1"/>
     <col min="2" max="2" width="24.625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="65.25" customWidth="1"/>
-    <col min="5" max="5" width="60.375" customWidth="1"/>
+    <col min="4" max="4" width="64.25" customWidth="1"/>
+    <col min="5" max="5" width="37.875" customWidth="1"/>
     <col min="6" max="6" width="20.375" customWidth="1"/>
     <col min="7" max="7" width="17.125" customWidth="1"/>
   </cols>
@@ -7418,78 +7443,297 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>150</v>
+      </c>
+      <c r="D3">
+        <v>160</v>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3">
+        <v>400</v>
+      </c>
+      <c r="G3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="C4">
+        <v>300</v>
+      </c>
+      <c r="D4">
+        <v>350</v>
+      </c>
+      <c r="E4">
+        <v>550</v>
+      </c>
+      <c r="F4">
+        <v>900</v>
+      </c>
+      <c r="G4">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>500</v>
+      </c>
+      <c r="D5">
+        <v>600</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
+        <v>1500</v>
+      </c>
+      <c r="G5">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>700</v>
+      </c>
+      <c r="D6">
+        <v>850</v>
+      </c>
+      <c r="E6">
+        <v>1450</v>
+      </c>
+      <c r="F6">
+        <v>2100</v>
+      </c>
+      <c r="G6">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>900</v>
+      </c>
+      <c r="D7">
+        <v>1100</v>
+      </c>
+      <c r="E7">
+        <v>1900</v>
+      </c>
+      <c r="F7">
+        <v>2700</v>
+      </c>
+      <c r="G7">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>900</v>
+      </c>
+      <c r="D8">
+        <v>1100</v>
+      </c>
+      <c r="E8">
+        <v>1900</v>
+      </c>
+      <c r="F8">
+        <v>2700</v>
+      </c>
+      <c r="G8">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>900</v>
+      </c>
+      <c r="D9">
+        <v>1100</v>
+      </c>
+      <c r="E9">
+        <v>1900</v>
+      </c>
+      <c r="F9">
+        <v>2700</v>
+      </c>
+      <c r="G9">
+        <v>3200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" ht="14.25" spans="1:27">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="X1" s="5"/>
       <c r="Y1" s="5"/>
@@ -7498,168 +7742,168 @@
     </row>
     <row r="2" ht="14.25" spans="1:27">
       <c r="A2" s="7" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="AA2" s="13" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
       <c r="A3" s="14" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="U3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="Y3" s="18" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="AA3" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -7667,7 +7911,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="C4" s="21">
         <v>10</v>
@@ -7723,16 +7967,16 @@
       <c r="V4" s="21"/>
       <c r="W4" s="23"/>
       <c r="X4" s="40" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="Y4" s="21" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z4" s="21" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -7740,7 +7984,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C5" s="26">
         <v>10</v>
@@ -7796,16 +8040,16 @@
       <c r="V5" s="26"/>
       <c r="W5" s="28"/>
       <c r="X5" s="29" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="Y5" s="26" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z5" s="26" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="AA5" s="28" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -7813,7 +8057,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C6" s="26">
         <v>10</v>
@@ -7869,16 +8113,16 @@
       <c r="V6" s="26"/>
       <c r="W6" s="28"/>
       <c r="X6" s="29" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z6" s="26" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="AA6" s="28" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -7886,7 +8130,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="C7" s="26">
         <v>10</v>
@@ -7942,16 +8186,16 @@
       <c r="V7" s="26"/>
       <c r="W7" s="28"/>
       <c r="X7" s="29" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="Y7" s="26" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z7" s="26" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="AA7" s="28" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -7959,7 +8203,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C8" s="26">
         <v>10</v>
@@ -8015,16 +8259,16 @@
       <c r="V8" s="26"/>
       <c r="W8" s="28"/>
       <c r="X8" s="29" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="Y8" s="26" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z8" s="26" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AA8" s="28" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -8032,7 +8276,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C9" s="26">
         <v>10</v>
@@ -8088,16 +8332,16 @@
       <c r="V9" s="26"/>
       <c r="W9" s="28"/>
       <c r="X9" s="29" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="Y9" s="26" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="Z9" s="26" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="AA9" s="28" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -8105,7 +8349,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C10" s="26">
         <v>10</v>
@@ -8161,16 +8405,16 @@
       <c r="V10" s="26"/>
       <c r="W10" s="28"/>
       <c r="X10" s="29" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="Y10" s="26" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="Z10" s="26" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="AA10" s="28" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -8178,7 +8422,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="C11" s="26">
         <v>10</v>
@@ -8234,16 +8478,16 @@
       <c r="V11" s="26"/>
       <c r="W11" s="28"/>
       <c r="X11" s="29" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="Y11" s="26" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="Z11" s="26" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="AA11" s="28" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -8251,7 +8495,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C12" s="26">
         <v>10</v>
@@ -8307,16 +8551,16 @@
       <c r="V12" s="26"/>
       <c r="W12" s="28"/>
       <c r="X12" s="29" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="Y12" s="26" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="Z12" s="26" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AA12" s="28" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -8324,7 +8568,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C13" s="26">
         <v>10</v>
@@ -8380,16 +8624,16 @@
       <c r="V13" s="26"/>
       <c r="W13" s="28"/>
       <c r="X13" s="29" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="Y13" s="26" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="Z13" s="26" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AA13" s="28" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -8397,7 +8641,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C14" s="26">
         <v>10</v>
@@ -8453,16 +8697,16 @@
       <c r="V14" s="26"/>
       <c r="W14" s="28"/>
       <c r="X14" s="29" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="Y14" s="26" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="Z14" s="26" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="AA14" s="28" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -8470,7 +8714,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C15" s="26">
         <v>10</v>
@@ -8526,16 +8770,16 @@
       <c r="V15" s="26"/>
       <c r="W15" s="28"/>
       <c r="X15" s="29" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="Y15" s="26" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="Z15" s="26" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="AA15" s="28" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -8543,7 +8787,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C16" s="26">
         <v>10</v>
@@ -8599,16 +8843,16 @@
       <c r="V16" s="26"/>
       <c r="W16" s="28"/>
       <c r="X16" s="29" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="Y16" s="26" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="Z16" s="26" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="AA16" s="28" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -8616,7 +8860,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C17" s="26">
         <v>10</v>
@@ -8672,16 +8916,16 @@
       <c r="V17" s="26"/>
       <c r="W17" s="28"/>
       <c r="X17" s="29" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="Y17" s="26" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="Z17" s="26" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AA17" s="28" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -8689,7 +8933,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C18" s="26">
         <v>10</v>
@@ -8745,16 +8989,16 @@
       <c r="V18" s="26"/>
       <c r="W18" s="28"/>
       <c r="X18" s="29" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="Y18" s="26" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="Z18" s="26" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="AA18" s="28" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -8762,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C19" s="26">
         <v>10</v>
@@ -8818,16 +9062,16 @@
       <c r="V19" s="26"/>
       <c r="W19" s="28"/>
       <c r="X19" s="29" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="Y19" s="26" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="Z19" s="26" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="AA19" s="28" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -8835,7 +9079,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C20" s="26">
         <v>10</v>
@@ -8891,16 +9135,16 @@
       <c r="V20" s="26"/>
       <c r="W20" s="28"/>
       <c r="X20" s="29" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="Y20" s="26" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="Z20" s="26" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AA20" s="28" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -8908,7 +9152,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C21" s="26">
         <v>10</v>
@@ -8964,16 +9208,16 @@
       <c r="V21" s="26"/>
       <c r="W21" s="28"/>
       <c r="X21" s="29" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="Y21" s="26" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="Z21" s="26" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="AA21" s="28" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -8981,7 +9225,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C22" s="26">
         <v>10</v>
@@ -9037,16 +9281,16 @@
       <c r="V22" s="26"/>
       <c r="W22" s="28"/>
       <c r="X22" s="29" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="Y22" s="26" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="Z22" s="26" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AA22" s="28" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -9054,7 +9298,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C23" s="26">
         <v>10</v>
@@ -9110,16 +9354,16 @@
       <c r="V23" s="26"/>
       <c r="W23" s="28"/>
       <c r="X23" s="29" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="Y23" s="26" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="Z23" s="26" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="AA23" s="28" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -9127,7 +9371,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="C24" s="26">
         <v>10</v>
@@ -9183,16 +9427,16 @@
       <c r="V24" s="26"/>
       <c r="W24" s="28"/>
       <c r="X24" s="29" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="Y24" s="26" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="Z24" s="26" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AA24" s="28" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -9200,7 +9444,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C25" s="26">
         <v>10</v>
@@ -9256,16 +9500,16 @@
       <c r="V25" s="26"/>
       <c r="W25" s="28"/>
       <c r="X25" s="29" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="Y25" s="26" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="Z25" s="26" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="AA25" s="28" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -9273,7 +9517,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C26" s="26">
         <v>10</v>
@@ -9329,16 +9573,16 @@
       <c r="V26" s="26"/>
       <c r="W26" s="28"/>
       <c r="X26" s="29" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="Y26" s="26" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="Z26" s="26" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="AA26" s="28" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -9346,7 +9590,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C27" s="26">
         <v>10</v>
@@ -9402,16 +9646,16 @@
       <c r="V27" s="26"/>
       <c r="W27" s="28"/>
       <c r="X27" s="29" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="Y27" s="26" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="Z27" s="26" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="AA27" s="28" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -9419,7 +9663,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C28" s="26">
         <v>10</v>
@@ -9475,16 +9719,16 @@
       <c r="V28" s="26"/>
       <c r="W28" s="28"/>
       <c r="X28" s="29" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="Y28" s="26" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="Z28" s="26" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AA28" s="28" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -9492,7 +9736,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="C29" s="26">
         <v>10</v>
@@ -9548,16 +9792,16 @@
       <c r="V29" s="26"/>
       <c r="W29" s="28"/>
       <c r="X29" s="29" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="Y29" s="26" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="Z29" s="26" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="AA29" s="28" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -9565,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C30" s="26">
         <v>10</v>
@@ -9621,16 +9865,16 @@
       <c r="V30" s="26"/>
       <c r="W30" s="28"/>
       <c r="X30" s="29" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="Y30" s="26" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="Z30" s="26" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AA30" s="28" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -9638,7 +9882,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C31" s="26">
         <v>10</v>
@@ -9694,16 +9938,16 @@
       <c r="V31" s="26"/>
       <c r="W31" s="28"/>
       <c r="X31" s="29" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="Y31" s="26" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="Z31" s="26" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AA31" s="28" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -9711,7 +9955,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C32" s="26">
         <v>10</v>
@@ -9767,16 +10011,16 @@
       <c r="V32" s="26"/>
       <c r="W32" s="28"/>
       <c r="X32" s="29" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="Y32" s="26" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="Z32" s="26" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="AA32" s="28" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -9784,7 +10028,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C33" s="26">
         <v>10</v>
@@ -9840,16 +10084,16 @@
       <c r="V33" s="26"/>
       <c r="W33" s="28"/>
       <c r="X33" s="29" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="Y33" s="26" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="Z33" s="26" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="AA33" s="28" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -9857,7 +10101,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="C34" s="26">
         <v>10</v>
@@ -9913,16 +10157,16 @@
       <c r="V34" s="26"/>
       <c r="W34" s="28"/>
       <c r="X34" s="29" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="Y34" s="26" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="Z34" s="26" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="AA34" s="28" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -9930,7 +10174,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="C35" s="26">
         <v>10</v>
@@ -9986,16 +10230,16 @@
       <c r="V35" s="26"/>
       <c r="W35" s="28"/>
       <c r="X35" s="29" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="Y35" s="26" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="Z35" s="26" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="AA35" s="28" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -10003,7 +10247,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="C36" s="26">
         <v>10</v>
@@ -10059,16 +10303,16 @@
       <c r="V36" s="26"/>
       <c r="W36" s="28"/>
       <c r="X36" s="29" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="Y36" s="26" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="Z36" s="26" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="AA36" s="28" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -10076,7 +10320,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="C37" s="26">
         <v>10</v>
@@ -10132,16 +10376,16 @@
       <c r="V37" s="26"/>
       <c r="W37" s="28"/>
       <c r="X37" s="29" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="Y37" s="26" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="Z37" s="26" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="AA37" s="28" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -10149,7 +10393,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="C38" s="26">
         <v>10</v>
@@ -10205,16 +10449,16 @@
       <c r="V38" s="26"/>
       <c r="W38" s="28"/>
       <c r="X38" s="29" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="Y38" s="26" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="Z38" s="26" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="AA38" s="28" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -10222,7 +10466,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="C39" s="26">
         <v>10</v>
@@ -10278,16 +10522,16 @@
       <c r="V39" s="26"/>
       <c r="W39" s="28"/>
       <c r="X39" s="29" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="Y39" s="26" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="Z39" s="26" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="AA39" s="28" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -10295,7 +10539,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="C40" s="26">
         <v>10</v>
@@ -10351,16 +10595,16 @@
       <c r="V40" s="26"/>
       <c r="W40" s="28"/>
       <c r="X40" s="29" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="Y40" s="26" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="Z40" s="26" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="AA40" s="28" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -10368,7 +10612,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="C41" s="31">
         <v>10</v>
@@ -10424,16 +10668,16 @@
       <c r="V41" s="31"/>
       <c r="W41" s="33"/>
       <c r="X41" s="34" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="Y41" s="31" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="Z41" s="31" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="AA41" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
